--- a/docs/PilotUsers/PilotUsersList.xlsx
+++ b/docs/PilotUsers/PilotUsersList.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\130010\Downloads\WorkerSalary-app-v4\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\136614\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7080" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16410" windowHeight="5325" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
     <sheet name="גיליון2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>ימי חג מותאמים לא מחושבים בניצול ימי חג, צריך להורידמסך ימי נחג שנותרו</t>
   </si>
@@ -101,6 +100,15 @@
   </si>
   <si>
     <t>SecSmadar01</t>
+  </si>
+  <si>
+    <t>אורנה עזר</t>
+  </si>
+  <si>
+    <t>OrnaA@metapel.com</t>
+  </si>
+  <si>
+    <t>SecOrnaA01</t>
   </si>
 </sst>
 </file>
@@ -167,16 +175,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="היפר-קישור" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -192,7 +203,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -455,13 +466,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="2">
         <v>1</v>
       </c>
@@ -469,7 +480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -477,7 +488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -485,7 +496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -493,7 +504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -501,7 +512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>6</v>
       </c>
@@ -509,7 +520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -517,7 +528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -534,14 +545,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>1</v>
       </c>
@@ -555,7 +566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -569,7 +580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -583,7 +594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -597,7 +608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -611,7 +622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -625,72 +636,81 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>20</v>
       </c>
@@ -703,8 +723,9 @@
     <hyperlink ref="C4" r:id="rId4"/>
     <hyperlink ref="C5" r:id="rId5"/>
     <hyperlink ref="C6" r:id="rId6"/>
+    <hyperlink ref="C7" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/docs/PilotUsers/PilotUsersList.xlsx
+++ b/docs/PilotUsers/PilotUsersList.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>ימי חג מותאמים לא מחושבים בניצול ימי חג, צריך להורידמסך ימי נחג שנותרו</t>
   </si>
@@ -109,6 +109,60 @@
   </si>
   <si>
     <t>SecOrnaA01</t>
+  </si>
+  <si>
+    <t>בטי מאיר</t>
+  </si>
+  <si>
+    <t>BettyM@metapek.com</t>
+  </si>
+  <si>
+    <t>SecBetty01</t>
+  </si>
+  <si>
+    <t>עינב מוזס</t>
+  </si>
+  <si>
+    <t>EinavM@metapel.com</t>
+  </si>
+  <si>
+    <t>SecEinav01</t>
+  </si>
+  <si>
+    <t>Ofra Deutsch</t>
+  </si>
+  <si>
+    <t>OfraD@metapel.com</t>
+  </si>
+  <si>
+    <t>SecOfra01</t>
+  </si>
+  <si>
+    <t>שרית ואבי טלקר</t>
+  </si>
+  <si>
+    <t>SaritAviT@metapel.com</t>
+  </si>
+  <si>
+    <t>SerSarit01</t>
+  </si>
+  <si>
+    <t>SigalitM@metapel.com</t>
+  </si>
+  <si>
+    <t>SecSigalit01</t>
+  </si>
+  <si>
+    <t>סיגלית משה</t>
+  </si>
+  <si>
+    <t>SoniaN@metapel.com</t>
+  </si>
+  <si>
+    <t>SecSonia01</t>
+  </si>
+  <si>
+    <t>סוניה כהן</t>
   </si>
 </sst>
 </file>
@@ -547,7 +601,7 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
@@ -654,30 +708,84 @@
       <c r="A8">
         <v>8</v>
       </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -724,8 +832,15 @@
     <hyperlink ref="C5" r:id="rId5"/>
     <hyperlink ref="C6" r:id="rId6"/>
     <hyperlink ref="C7" r:id="rId7"/>
+    <hyperlink ref="C8" r:id="rId8"/>
+    <hyperlink ref="C9" r:id="rId9"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.facebook.com/groups/701329108383911/user/100005207651173/?__cft__%5b0%5d=AZZc6GMTYp0YxkGYd0jjx3Lxfb-Hs1uN43KfeAYE4lVamYDSytGgrVDyrU59kcPJGN5zENRvOd1Ru9bQl5Bu-_PkZBzQMbLLs6IjL_FoTviPmDV6hIgTb-C-evI33g5FpqYr7RbAADyeUdHN85Mq5y7X&amp;__tn__=-a-R"/>
+    <hyperlink ref="C10" r:id="rId11"/>
+    <hyperlink ref="C11" r:id="rId12"/>
+    <hyperlink ref="C12" r:id="rId13"/>
+    <hyperlink ref="C13" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>